--- a/data/trans_orig/P39C-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P39C-Habitat-trans_orig.xlsx
@@ -536,7 +536,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según el tiempo transcurrido desde la última vez que le midieron la glucosa en 2016</t>
+          <t>Población según el tiempo transcurrido desde la última vez que le midieron la glucosa en 2016 (tasa de respuesta: 97,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -731,12 +731,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>52917</t>
+          <t>52877</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>85053</t>
+          <t>85159</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -751,7 +751,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>16,13%</t>
+          <t>16,15%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -766,12 +766,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>33955</t>
+          <t>34319</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>59435</t>
+          <t>59271</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -781,12 +781,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>6,03%</t>
+          <t>6,09%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>10,55%</t>
+          <t>10,53%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -801,12 +801,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>96298</t>
+          <t>95619</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>137303</t>
+          <t>136080</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -816,12 +816,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>8,83%</t>
+          <t>8,77%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>12,59%</t>
+          <t>12,48%</t>
         </is>
       </c>
     </row>
@@ -844,12 +844,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>108004</t>
+          <t>108950</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>148691</t>
+          <t>149277</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -859,12 +859,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>20,48%</t>
+          <t>20,66%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>28,19%</t>
+          <t>28,31%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -879,12 +879,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>106467</t>
+          <t>108399</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>147279</t>
+          <t>147638</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -894,12 +894,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>18,91%</t>
+          <t>19,25%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>26,15%</t>
+          <t>26,22%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -914,12 +914,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>230026</t>
+          <t>227206</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>285183</t>
+          <t>282653</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -929,12 +929,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>21,09%</t>
+          <t>20,84%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>26,15%</t>
+          <t>25,92%</t>
         </is>
       </c>
     </row>
@@ -957,12 +957,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>130613</t>
+          <t>129913</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>173121</t>
+          <t>171738</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -972,12 +972,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>24,77%</t>
+          <t>24,63%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>32,83%</t>
+          <t>32,56%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>141059</t>
+          <t>142239</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>186400</t>
+          <t>184292</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>25,05%</t>
+          <t>25,26%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>33,1%</t>
+          <t>32,73%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>279706</t>
+          <t>281755</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>340255</t>
+          <t>343235</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1042,12 +1042,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>25,65%</t>
+          <t>25,84%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>31,2%</t>
+          <t>31,48%</t>
         </is>
       </c>
     </row>
@@ -1070,12 +1070,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>63923</t>
+          <t>64397</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>97330</t>
+          <t>97849</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1085,12 +1085,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>12,12%</t>
+          <t>12,21%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>18,46%</t>
+          <t>18,55%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1105,12 +1105,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>70598</t>
+          <t>72897</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>105515</t>
+          <t>106022</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1120,12 +1120,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>12,54%</t>
+          <t>12,95%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>18,74%</t>
+          <t>18,83%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1140,12 +1140,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>146296</t>
+          <t>144769</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>194417</t>
+          <t>193545</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1155,12 +1155,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>13,42%</t>
+          <t>13,28%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>17,83%</t>
+          <t>17,75%</t>
         </is>
       </c>
     </row>
@@ -1183,12 +1183,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>82614</t>
+          <t>81077</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>118699</t>
+          <t>117726</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1198,12 +1198,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>15,67%</t>
+          <t>15,37%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>22,51%</t>
+          <t>22,32%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1218,12 +1218,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>121095</t>
+          <t>121093</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>161132</t>
+          <t>163763</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1233,12 +1233,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>21,51%</t>
+          <t>21,5%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>28,62%</t>
+          <t>29,08%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1253,12 +1253,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>211277</t>
+          <t>211157</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>265270</t>
+          <t>269146</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1268,12 +1268,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>19,37%</t>
+          <t>19,36%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>24,33%</t>
+          <t>24,68%</t>
         </is>
       </c>
     </row>
@@ -1413,12 +1413,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>90852</t>
+          <t>93601</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>132492</t>
+          <t>133120</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1428,12 +1428,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>11,21%</t>
+          <t>11,55%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>16,35%</t>
+          <t>16,42%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1448,12 +1448,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>77591</t>
+          <t>78942</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>113341</t>
+          <t>116329</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1463,12 +1463,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>8,43%</t>
+          <t>8,58%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>12,32%</t>
+          <t>12,64%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1483,12 +1483,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>180919</t>
+          <t>179262</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>237308</t>
+          <t>236632</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1498,12 +1498,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>10,46%</t>
+          <t>10,36%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>13,71%</t>
+          <t>13,67%</t>
         </is>
       </c>
     </row>
@@ -1526,12 +1526,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>177673</t>
+          <t>174640</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>226327</t>
+          <t>227985</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1541,12 +1541,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>21,92%</t>
+          <t>21,55%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>27,93%</t>
+          <t>28,13%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1561,12 +1561,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>218568</t>
+          <t>217532</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>272161</t>
+          <t>273803</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1576,12 +1576,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>23,76%</t>
+          <t>23,65%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>29,58%</t>
+          <t>29,76%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1596,12 +1596,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>408629</t>
+          <t>404435</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>482161</t>
+          <t>482320</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1611,12 +1611,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>23,61%</t>
+          <t>23,37%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>27,86%</t>
+          <t>27,87%</t>
         </is>
       </c>
     </row>
@@ -1639,12 +1639,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>216290</t>
+          <t>216233</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>267123</t>
+          <t>269122</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1654,12 +1654,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>26,69%</t>
+          <t>26,68%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>32,96%</t>
+          <t>33,21%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1674,12 +1674,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>245511</t>
+          <t>245334</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>300221</t>
+          <t>300490</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1689,12 +1689,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>26,69%</t>
+          <t>26,67%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>32,63%</t>
+          <t>32,66%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1709,12 +1709,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>477372</t>
+          <t>477303</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>556060</t>
+          <t>554062</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1724,12 +1724,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>27,59%</t>
+          <t>27,58%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>32,13%</t>
+          <t>32,02%</t>
         </is>
       </c>
     </row>
@@ -1752,12 +1752,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>89869</t>
+          <t>91772</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>133950</t>
+          <t>133696</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1767,12 +1767,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>11,09%</t>
+          <t>11,32%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>16,53%</t>
+          <t>16,5%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1787,12 +1787,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>109330</t>
+          <t>109687</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>154404</t>
+          <t>152484</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1802,12 +1802,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>11,88%</t>
+          <t>11,92%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>16,78%</t>
+          <t>16,57%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1822,12 +1822,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>212204</t>
+          <t>213944</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>272034</t>
+          <t>274170</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1837,12 +1837,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>12,26%</t>
+          <t>12,36%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>15,72%</t>
+          <t>15,84%</t>
         </is>
       </c>
     </row>
@@ -1865,12 +1865,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>123055</t>
+          <t>124049</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>168392</t>
+          <t>168127</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1880,12 +1880,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>15,18%</t>
+          <t>15,31%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>20,78%</t>
+          <t>20,74%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1900,12 +1900,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>155349</t>
+          <t>152148</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>204293</t>
+          <t>203353</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1915,12 +1915,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>16,89%</t>
+          <t>16,54%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>22,21%</t>
+          <t>22,1%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1935,12 +1935,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>288080</t>
+          <t>292689</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>354956</t>
+          <t>357195</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1950,12 +1950,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>16,65%</t>
+          <t>16,91%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>20,51%</t>
+          <t>20,64%</t>
         </is>
       </c>
     </row>
@@ -2095,12 +2095,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>37953</t>
+          <t>39236</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>66233</t>
+          <t>67871</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2110,12 +2110,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>6,57%</t>
+          <t>6,79%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>11,47%</t>
+          <t>11,75%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2130,12 +2130,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>38840</t>
+          <t>39004</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>66142</t>
+          <t>66340</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2145,12 +2145,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>5,81%</t>
+          <t>5,84%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>9,9%</t>
+          <t>9,93%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2165,12 +2165,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>82850</t>
+          <t>84314</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>122609</t>
+          <t>123759</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>6,65%</t>
+          <t>6,77%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>9,84%</t>
+          <t>9,94%</t>
         </is>
       </c>
     </row>
@@ -2208,12 +2208,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>167254</t>
+          <t>167461</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>213354</t>
+          <t>213683</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2223,12 +2223,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>28,96%</t>
+          <t>28,99%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>36,94%</t>
+          <t>37,0%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2243,12 +2243,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>156544</t>
+          <t>155873</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>203223</t>
+          <t>200536</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2258,12 +2258,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>23,43%</t>
+          <t>23,33%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>30,42%</t>
+          <t>30,02%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2278,12 +2278,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>332751</t>
+          <t>335719</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>398525</t>
+          <t>403619</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2293,12 +2293,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>26,71%</t>
+          <t>26,95%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>31,99%</t>
+          <t>32,4%</t>
         </is>
       </c>
     </row>
@@ -2321,12 +2321,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>155969</t>
+          <t>156224</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>205820</t>
+          <t>202338</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2336,12 +2336,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>27,0%</t>
+          <t>27,05%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>35,64%</t>
+          <t>35,03%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2356,12 +2356,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>204665</t>
+          <t>203866</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>256018</t>
+          <t>253736</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2371,12 +2371,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>30,63%</t>
+          <t>30,51%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>38,32%</t>
+          <t>37,98%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2391,12 +2391,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>373411</t>
+          <t>374213</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>445370</t>
+          <t>441109</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2406,12 +2406,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>29,98%</t>
+          <t>30,04%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>35,75%</t>
+          <t>35,41%</t>
         </is>
       </c>
     </row>
@@ -2434,12 +2434,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>50363</t>
+          <t>51373</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>82504</t>
+          <t>84952</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>8,72%</t>
+          <t>8,89%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>14,28%</t>
+          <t>14,71%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2469,12 +2469,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>58311</t>
+          <t>57053</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>91533</t>
+          <t>94697</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2484,12 +2484,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>8,73%</t>
+          <t>8,54%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>13,7%</t>
+          <t>14,17%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2504,12 +2504,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>118580</t>
+          <t>119134</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>163112</t>
+          <t>166459</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2519,12 +2519,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>9,52%</t>
+          <t>9,56%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>13,09%</t>
+          <t>13,36%</t>
         </is>
       </c>
     </row>
@@ -2547,12 +2547,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>74437</t>
+          <t>73046</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>111279</t>
+          <t>111391</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2562,12 +2562,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>12,89%</t>
+          <t>12,65%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>19,27%</t>
+          <t>19,29%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2582,12 +2582,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>116877</t>
+          <t>116118</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>158214</t>
+          <t>159567</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2597,12 +2597,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>17,49%</t>
+          <t>17,38%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>23,68%</t>
+          <t>23,88%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2617,12 +2617,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>200765</t>
+          <t>201997</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>256466</t>
+          <t>258152</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2632,12 +2632,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>16,12%</t>
+          <t>16,22%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>20,59%</t>
+          <t>20,72%</t>
         </is>
       </c>
     </row>
@@ -2777,12 +2777,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>65868</t>
+          <t>66653</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>100288</t>
+          <t>100923</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2792,12 +2792,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>9,1%</t>
+          <t>9,21%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>13,86%</t>
+          <t>13,95%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2812,12 +2812,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>45274</t>
+          <t>45873</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>75968</t>
+          <t>76407</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2827,12 +2827,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>5,29%</t>
+          <t>5,36%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>8,88%</t>
+          <t>8,93%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2847,12 +2847,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>119614</t>
+          <t>118314</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>163285</t>
+          <t>165037</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2862,12 +2862,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>7,57%</t>
+          <t>7,49%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>10,34%</t>
+          <t>10,45%</t>
         </is>
       </c>
     </row>
@@ -2890,12 +2890,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>185785</t>
+          <t>185949</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>234745</t>
+          <t>233155</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2905,12 +2905,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>25,68%</t>
+          <t>25,7%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>32,45%</t>
+          <t>32,23%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2925,12 +2925,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>202779</t>
+          <t>202383</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>256153</t>
+          <t>257240</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2940,12 +2940,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>23,69%</t>
+          <t>23,65%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>29,93%</t>
+          <t>30,05%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2960,12 +2960,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>405341</t>
+          <t>401473</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>475488</t>
+          <t>475029</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2975,12 +2975,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>25,66%</t>
+          <t>25,42%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>30,11%</t>
+          <t>30,08%</t>
         </is>
       </c>
     </row>
@@ -3003,12 +3003,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>169221</t>
+          <t>168882</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>216728</t>
+          <t>216908</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3018,12 +3018,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>23,39%</t>
+          <t>23,34%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>29,96%</t>
+          <t>29,98%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3038,12 +3038,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>226623</t>
+          <t>224799</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>281519</t>
+          <t>282994</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3053,12 +3053,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>26,48%</t>
+          <t>26,26%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>32,89%</t>
+          <t>33,06%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3073,12 +3073,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>410005</t>
+          <t>409914</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>484907</t>
+          <t>482583</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3088,12 +3088,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>25,96%</t>
+          <t>25,95%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>30,7%</t>
+          <t>30,56%</t>
         </is>
       </c>
     </row>
@@ -3116,12 +3116,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>87595</t>
+          <t>88349</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>126624</t>
+          <t>128272</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3131,12 +3131,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>12,11%</t>
+          <t>12,21%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>17,5%</t>
+          <t>17,73%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3151,12 +3151,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>114234</t>
+          <t>116098</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>159899</t>
+          <t>161498</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3166,12 +3166,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>13,35%</t>
+          <t>13,56%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>18,68%</t>
+          <t>18,87%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3186,12 +3186,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>215239</t>
+          <t>214184</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>278400</t>
+          <t>274519</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3201,12 +3201,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>13,63%</t>
+          <t>13,56%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>17,63%</t>
+          <t>17,38%</t>
         </is>
       </c>
     </row>
@@ -3229,12 +3229,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>115409</t>
+          <t>113936</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>155968</t>
+          <t>155726</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3244,12 +3244,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>15,95%</t>
+          <t>15,75%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>21,56%</t>
+          <t>21,52%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3264,12 +3264,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>153437</t>
+          <t>151152</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>201892</t>
+          <t>203820</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3279,12 +3279,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>17,93%</t>
+          <t>17,66%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>23,59%</t>
+          <t>23,81%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3299,12 +3299,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>280143</t>
+          <t>278104</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>345334</t>
+          <t>342171</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3314,12 +3314,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>17,74%</t>
+          <t>17,61%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>21,87%</t>
+          <t>21,66%</t>
         </is>
       </c>
     </row>
@@ -3459,12 +3459,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>281520</t>
+          <t>279654</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>350513</t>
+          <t>348754</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3474,12 +3474,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>10,67%</t>
+          <t>10,6%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>13,28%</t>
+          <t>13,22%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3494,12 +3494,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>221858</t>
+          <t>221359</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>284715</t>
+          <t>283908</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3509,12 +3509,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>7,38%</t>
+          <t>7,36%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>9,47%</t>
+          <t>9,44%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3529,12 +3529,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>516579</t>
+          <t>521810</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>611179</t>
+          <t>612555</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3544,12 +3544,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>9,15%</t>
+          <t>9,24%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>10,83%</t>
+          <t>10,85%</t>
         </is>
       </c>
     </row>
@@ -3572,12 +3572,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>680673</t>
+          <t>680428</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>773417</t>
+          <t>773753</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3587,12 +3587,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>25,79%</t>
+          <t>25,78%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>29,31%</t>
+          <t>29,32%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3607,12 +3607,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>733677</t>
+          <t>732802</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>833040</t>
+          <t>830799</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3622,12 +3622,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>24,4%</t>
+          <t>24,37%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>27,7%</t>
+          <t>27,63%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3642,12 +3642,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>1435423</t>
+          <t>1438837</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>1571228</t>
+          <t>1572458</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3657,12 +3657,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>25,42%</t>
+          <t>25,48%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>27,83%</t>
+          <t>27,85%</t>
         </is>
       </c>
     </row>
@@ -3685,12 +3685,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>721375</t>
+          <t>720362</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>816625</t>
+          <t>815338</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3700,12 +3700,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>27,34%</t>
+          <t>27,3%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>30,95%</t>
+          <t>30,9%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3720,12 +3720,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>865630</t>
+          <t>865861</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>967719</t>
+          <t>964915</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3740,7 +3740,7 @@
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>32,18%</t>
+          <t>32,09%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3755,12 +3755,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>1618075</t>
+          <t>1613853</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>1758349</t>
+          <t>1752680</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3770,12 +3770,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>28,66%</t>
+          <t>28,58%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>31,14%</t>
+          <t>31,04%</t>
         </is>
       </c>
     </row>
@@ -3798,12 +3798,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>326974</t>
+          <t>330688</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>405139</t>
+          <t>404019</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3813,12 +3813,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>12,39%</t>
+          <t>12,53%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>15,35%</t>
+          <t>15,31%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3833,12 +3833,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>384799</t>
+          <t>389115</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>469729</t>
+          <t>470399</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3848,12 +3848,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>12,8%</t>
+          <t>12,94%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>15,62%</t>
+          <t>15,64%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3868,12 +3868,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>742969</t>
+          <t>740085</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>849474</t>
+          <t>846161</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3883,12 +3883,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>13,16%</t>
+          <t>13,11%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>15,05%</t>
+          <t>14,99%</t>
         </is>
       </c>
     </row>
@@ -3911,12 +3911,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>432525</t>
+          <t>432030</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>508543</t>
+          <t>510298</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3926,12 +3926,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>16,39%</t>
+          <t>16,37%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>19,27%</t>
+          <t>19,34%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3946,12 +3946,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>586564</t>
+          <t>585361</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>678512</t>
+          <t>677930</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3961,12 +3961,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>19,51%</t>
+          <t>19,47%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>22,56%</t>
+          <t>22,54%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3981,12 +3981,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>1039868</t>
+          <t>1040577</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>1163914</t>
+          <t>1165572</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -3996,12 +3996,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>18,42%</t>
+          <t>18,43%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>20,61%</t>
+          <t>20,64%</t>
         </is>
       </c>
     </row>
@@ -4178,7 +4178,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según el tiempo transcurrido desde la última vez que le midieron la glucosa en 2023</t>
+          <t>Población según el tiempo transcurrido desde la última vez que le midieron la glucosa en 2023 (tasa de respuesta: 99,23%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -4373,12 +4373,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>36044</t>
+          <t>37092</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>63549</t>
+          <t>66552</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4388,12 +4388,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>6,65%</t>
+          <t>6,84%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>11,72%</t>
+          <t>12,28%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4408,12 +4408,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>49819</t>
+          <t>50271</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>75605</t>
+          <t>78001</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4423,12 +4423,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>8,08%</t>
+          <t>8,15%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>12,26%</t>
+          <t>12,65%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4443,12 +4443,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>92954</t>
+          <t>92143</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>131866</t>
+          <t>132811</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4458,12 +4458,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>8,02%</t>
+          <t>7,95%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>11,38%</t>
+          <t>11,46%</t>
         </is>
       </c>
     </row>
@@ -4486,12 +4486,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>108271</t>
+          <t>108149</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>151018</t>
+          <t>148244</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4501,12 +4501,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>19,98%</t>
+          <t>19,95%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>27,86%</t>
+          <t>27,35%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4521,12 +4521,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>108864</t>
+          <t>108974</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>141450</t>
+          <t>140998</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4536,12 +4536,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>17,65%</t>
+          <t>17,67%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>22,94%</t>
+          <t>22,86%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4556,12 +4556,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>229535</t>
+          <t>226452</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>280605</t>
+          <t>278921</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4571,12 +4571,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>19,81%</t>
+          <t>19,54%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>24,22%</t>
+          <t>24,07%</t>
         </is>
       </c>
     </row>
@@ -4599,12 +4599,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>123417</t>
+          <t>123249</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>164745</t>
+          <t>166471</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -4614,12 +4614,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>22,77%</t>
+          <t>22,74%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>30,39%</t>
+          <t>30,71%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -4634,12 +4634,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>144100</t>
+          <t>143759</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>178556</t>
+          <t>178636</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4649,12 +4649,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>23,36%</t>
+          <t>23,31%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>28,95%</t>
+          <t>28,96%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -4669,12 +4669,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>278199</t>
+          <t>277110</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>333091</t>
+          <t>329137</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4684,12 +4684,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>24,01%</t>
+          <t>23,91%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>28,75%</t>
+          <t>28,4%</t>
         </is>
       </c>
     </row>
@@ -4712,12 +4712,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>87868</t>
+          <t>89046</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>123468</t>
+          <t>124144</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4727,12 +4727,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>16,21%</t>
+          <t>16,43%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>22,78%</t>
+          <t>22,9%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4747,12 +4747,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>101699</t>
+          <t>102109</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>132011</t>
+          <t>132224</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4762,12 +4762,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>16,49%</t>
+          <t>16,56%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>21,4%</t>
+          <t>21,44%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4782,12 +4782,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>197654</t>
+          <t>200467</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>243773</t>
+          <t>243560</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4797,12 +4797,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>17,06%</t>
+          <t>17,3%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>21,04%</t>
+          <t>21,02%</t>
         </is>
       </c>
     </row>
@@ -4825,12 +4825,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>98079</t>
+          <t>99911</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>136506</t>
+          <t>136163</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4840,12 +4840,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>18,09%</t>
+          <t>18,43%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>25,18%</t>
+          <t>25,12%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4860,12 +4860,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>139598</t>
+          <t>138113</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>173486</t>
+          <t>172010</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4875,12 +4875,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>22,63%</t>
+          <t>22,39%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>28,13%</t>
+          <t>27,89%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4895,12 +4895,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>244198</t>
+          <t>245554</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>298187</t>
+          <t>296813</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4910,12 +4910,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>21,07%</t>
+          <t>21,19%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>25,73%</t>
+          <t>25,61%</t>
         </is>
       </c>
     </row>
@@ -5055,12 +5055,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>55378</t>
+          <t>56917</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>96921</t>
+          <t>92272</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5070,12 +5070,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>7,73%</t>
+          <t>7,94%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>13,52%</t>
+          <t>12,87%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5090,12 +5090,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>44308</t>
+          <t>44512</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>70796</t>
+          <t>69934</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5105,12 +5105,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>5,49%</t>
+          <t>5,52%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>8,78%</t>
+          <t>8,67%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5125,12 +5125,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>107359</t>
+          <t>105602</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>152285</t>
+          <t>151453</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5140,12 +5140,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>7,05%</t>
+          <t>6,93%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>10,0%</t>
+          <t>9,94%</t>
         </is>
       </c>
     </row>
@@ -5168,12 +5168,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>134651</t>
+          <t>134006</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>180778</t>
+          <t>179748</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5183,12 +5183,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>18,79%</t>
+          <t>18,7%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>25,22%</t>
+          <t>25,08%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -5203,12 +5203,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>180076</t>
+          <t>180353</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>220489</t>
+          <t>224336</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5218,12 +5218,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>22,33%</t>
+          <t>22,36%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>27,34%</t>
+          <t>27,82%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5238,12 +5238,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>328181</t>
+          <t>323635</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>388327</t>
+          <t>386311</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5253,12 +5253,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>21,55%</t>
+          <t>21,25%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>25,49%</t>
+          <t>25,36%</t>
         </is>
       </c>
     </row>
@@ -5281,12 +5281,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>206472</t>
+          <t>203247</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>262208</t>
+          <t>258498</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -5296,12 +5296,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>28,81%</t>
+          <t>28,36%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>36,58%</t>
+          <t>36,06%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -5316,12 +5316,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>201338</t>
+          <t>199221</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>241187</t>
+          <t>240702</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5331,12 +5331,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>24,97%</t>
+          <t>24,7%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>29,91%</t>
+          <t>29,85%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -5351,12 +5351,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>413642</t>
+          <t>418913</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>488768</t>
+          <t>488498</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -5366,12 +5366,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>27,16%</t>
+          <t>27,5%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>32,09%</t>
+          <t>32,07%</t>
         </is>
       </c>
     </row>
@@ -5394,12 +5394,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>98623</t>
+          <t>99287</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>140680</t>
+          <t>140240</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5409,12 +5409,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>13,76%</t>
+          <t>13,85%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>19,63%</t>
+          <t>19,56%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5429,12 +5429,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>115894</t>
+          <t>116668</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>148183</t>
+          <t>149749</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5444,12 +5444,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>14,37%</t>
+          <t>14,47%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>18,38%</t>
+          <t>18,57%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5464,12 +5464,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>223387</t>
+          <t>223414</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>278924</t>
+          <t>279135</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5484,7 +5484,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>18,31%</t>
+          <t>18,33%</t>
         </is>
       </c>
     </row>
@@ -5507,12 +5507,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>118230</t>
+          <t>119273</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>161579</t>
+          <t>161151</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5522,12 +5522,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>16,49%</t>
+          <t>16,64%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>22,54%</t>
+          <t>22,48%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5542,12 +5542,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>176676</t>
+          <t>177301</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>220135</t>
+          <t>219594</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5557,12 +5557,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>21,91%</t>
+          <t>21,99%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>27,3%</t>
+          <t>27,23%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5577,12 +5577,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>308894</t>
+          <t>307752</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>368188</t>
+          <t>371835</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5592,12 +5592,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>20,28%</t>
+          <t>20,2%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>24,17%</t>
+          <t>24,41%</t>
         </is>
       </c>
     </row>
@@ -5737,12 +5737,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>36603</t>
+          <t>36410</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>70217</t>
+          <t>71591</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5752,12 +5752,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>6,59%</t>
+          <t>6,56%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>12,64%</t>
+          <t>12,89%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5772,12 +5772,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>21156</t>
+          <t>20012</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>65384</t>
+          <t>64748</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5787,12 +5787,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>2,55%</t>
+          <t>2,42%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>7,89%</t>
+          <t>7,82%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5807,12 +5807,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>57110</t>
+          <t>56972</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>123019</t>
+          <t>124064</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5822,12 +5822,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>4,13%</t>
+          <t>4,12%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>8,89%</t>
+          <t>8,97%</t>
         </is>
       </c>
     </row>
@@ -5850,12 +5850,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>170000</t>
+          <t>168340</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>217351</t>
+          <t>217314</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5865,12 +5865,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>30,61%</t>
+          <t>30,31%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>39,14%</t>
+          <t>39,13%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>92991</t>
+          <t>82173</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>253277</t>
+          <t>254599</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5900,12 +5900,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>11,23%</t>
+          <t>9,92%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>30,58%</t>
+          <t>30,74%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5920,12 +5920,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>228458</t>
+          <t>225906</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>455274</t>
+          <t>458315</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5935,12 +5935,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>16,51%</t>
+          <t>16,33%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>32,9%</t>
+          <t>33,12%</t>
         </is>
       </c>
     </row>
@@ -5963,12 +5963,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>131481</t>
+          <t>130773</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>179035</t>
+          <t>176613</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -5978,12 +5978,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>23,68%</t>
+          <t>23,55%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>32,24%</t>
+          <t>31,8%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -5998,12 +5998,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>262416</t>
+          <t>262759</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>614000</t>
+          <t>644720</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -6013,12 +6013,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>31,68%</t>
+          <t>31,72%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>74,12%</t>
+          <t>77,83%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -6033,12 +6033,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>408718</t>
+          <t>401469</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>885521</t>
+          <t>887333</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -6048,12 +6048,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>29,54%</t>
+          <t>29,01%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>64,0%</t>
+          <t>64,13%</t>
         </is>
       </c>
     </row>
@@ -6076,12 +6076,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>54627</t>
+          <t>55618</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>86705</t>
+          <t>88778</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -6091,12 +6091,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>9,84%</t>
+          <t>10,02%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>15,61%</t>
+          <t>15,99%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -6111,12 +6111,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>34586</t>
+          <t>34064</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>103249</t>
+          <t>103576</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -6126,12 +6126,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>4,18%</t>
+          <t>4,11%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>12,46%</t>
+          <t>12,5%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -6146,12 +6146,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>79856</t>
+          <t>84623</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>175051</t>
+          <t>179665</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -6161,12 +6161,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>5,77%</t>
+          <t>6,12%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>12,65%</t>
+          <t>12,98%</t>
         </is>
       </c>
     </row>
@@ -6189,12 +6189,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>73199</t>
+          <t>73294</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>106932</t>
+          <t>108190</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -6204,12 +6204,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>13,18%</t>
+          <t>13,2%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>19,26%</t>
+          <t>19,48%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -6224,12 +6224,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>55745</t>
+          <t>51599</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>158625</t>
+          <t>157862</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -6239,12 +6239,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>6,73%</t>
+          <t>6,23%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>19,15%</t>
+          <t>19,06%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -6259,12 +6259,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>117789</t>
+          <t>128652</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>248914</t>
+          <t>249390</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -6274,12 +6274,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>8,51%</t>
+          <t>9,3%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>17,99%</t>
+          <t>18,02%</t>
         </is>
       </c>
     </row>
@@ -6419,12 +6419,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>34901</t>
+          <t>35110</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>63139</t>
+          <t>63289</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6434,12 +6434,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>4,73%</t>
+          <t>4,76%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>8,55%</t>
+          <t>8,57%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6454,12 +6454,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>39867</t>
+          <t>40615</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>65701</t>
+          <t>64781</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6469,12 +6469,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>4,52%</t>
+          <t>4,61%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>7,45%</t>
+          <t>7,35%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6489,12 +6489,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>80927</t>
+          <t>80803</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>121965</t>
+          <t>119012</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6504,12 +6504,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>5,0%</t>
+          <t>4,99%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>7,53%</t>
+          <t>7,35%</t>
         </is>
       </c>
     </row>
@@ -6532,12 +6532,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>166663</t>
+          <t>166692</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>219789</t>
+          <t>219809</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -6567,12 +6567,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>174764</t>
+          <t>175302</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>217243</t>
+          <t>215457</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -6582,12 +6582,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>19,83%</t>
+          <t>19,89%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>24,65%</t>
+          <t>24,44%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -6602,12 +6602,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>355200</t>
+          <t>353069</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>425197</t>
+          <t>420853</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -6617,12 +6617,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>21,93%</t>
+          <t>21,8%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>26,25%</t>
+          <t>25,99%</t>
         </is>
       </c>
     </row>
@@ -6645,12 +6645,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>202248</t>
+          <t>204310</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>255730</t>
+          <t>253575</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -6660,12 +6660,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>27,4%</t>
+          <t>27,68%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>34,65%</t>
+          <t>34,35%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -6680,12 +6680,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>266292</t>
+          <t>266599</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>311884</t>
+          <t>311518</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -6695,12 +6695,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>30,21%</t>
+          <t>30,25%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>35,38%</t>
+          <t>35,34%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -6715,12 +6715,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>480034</t>
+          <t>482355</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>551267</t>
+          <t>553269</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -6730,12 +6730,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>29,64%</t>
+          <t>29,78%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>34,04%</t>
+          <t>34,16%</t>
         </is>
       </c>
     </row>
@@ -6758,12 +6758,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>113147</t>
+          <t>113367</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>156037</t>
+          <t>155130</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6773,12 +6773,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>15,33%</t>
+          <t>15,36%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>21,14%</t>
+          <t>21,02%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6793,12 +6793,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>132096</t>
+          <t>134105</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>169073</t>
+          <t>171907</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6808,12 +6808,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>14,99%</t>
+          <t>15,21%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>19,18%</t>
+          <t>19,5%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6828,12 +6828,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>257303</t>
+          <t>257327</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>310018</t>
+          <t>314330</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6848,7 +6848,7 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>19,14%</t>
+          <t>19,41%</t>
         </is>
       </c>
     </row>
@@ -6871,12 +6871,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>117186</t>
+          <t>118538</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>160386</t>
+          <t>159990</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6886,12 +6886,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>15,88%</t>
+          <t>16,06%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>21,73%</t>
+          <t>21,67%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6906,12 +6906,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>176472</t>
+          <t>177137</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>219122</t>
+          <t>218822</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6921,12 +6921,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>20,02%</t>
+          <t>20,1%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>24,86%</t>
+          <t>24,83%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6941,12 +6941,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>307149</t>
+          <t>308239</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>366158</t>
+          <t>366668</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6956,12 +6956,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>18,96%</t>
+          <t>19,03%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>22,61%</t>
+          <t>22,64%</t>
         </is>
       </c>
     </row>
@@ -7101,12 +7101,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>188895</t>
+          <t>189985</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>252832</t>
+          <t>253249</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -7116,12 +7116,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>7,4%</t>
+          <t>7,44%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>9,91%</t>
+          <t>9,92%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -7136,12 +7136,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>170455</t>
+          <t>169140</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>243935</t>
+          <t>245341</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -7151,12 +7151,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>5,44%</t>
+          <t>5,4%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>7,79%</t>
+          <t>7,83%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -7171,12 +7171,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>370556</t>
+          <t>376305</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>476555</t>
+          <t>477555</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -7186,12 +7186,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>6,52%</t>
+          <t>6,62%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>8,38%</t>
+          <t>8,4%</t>
         </is>
       </c>
     </row>
@@ -7214,12 +7214,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>619599</t>
+          <t>624114</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>716986</t>
+          <t>719194</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -7229,12 +7229,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>24,28%</t>
+          <t>24,45%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>28,09%</t>
+          <t>28,18%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -7249,12 +7249,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>539355</t>
+          <t>514877</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>763920</t>
+          <t>764924</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -7264,12 +7264,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>17,22%</t>
+          <t>16,43%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>24,38%</t>
+          <t>24,42%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -7284,12 +7284,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>1198886</t>
+          <t>1198206</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>1452057</t>
+          <t>1452035</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -7299,7 +7299,7 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>21,09%</t>
+          <t>21,08%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
@@ -7327,12 +7327,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>708105</t>
+          <t>709204</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>805649</t>
+          <t>807642</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -7342,12 +7342,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>27,74%</t>
+          <t>27,79%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>31,57%</t>
+          <t>31,64%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -7362,12 +7362,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>923479</t>
+          <t>917760</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>1571757</t>
+          <t>1561249</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -7377,12 +7377,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>29,48%</t>
+          <t>29,29%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>50,17%</t>
+          <t>49,83%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -7397,12 +7397,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>1669950</t>
+          <t>1666576</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>2346436</t>
+          <t>2360790</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -7412,12 +7412,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>29,37%</t>
+          <t>29,31%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>41,27%</t>
+          <t>41,53%</t>
         </is>
       </c>
     </row>
@@ -7440,12 +7440,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>386905</t>
+          <t>388860</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>466108</t>
+          <t>465000</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -7455,12 +7455,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>15,16%</t>
+          <t>15,24%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>18,26%</t>
+          <t>18,22%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -7475,12 +7475,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>360904</t>
+          <t>371900</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>519477</t>
+          <t>521615</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -7490,12 +7490,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>11,52%</t>
+          <t>11,87%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>16,58%</t>
+          <t>16,65%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -7510,12 +7510,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>784907</t>
+          <t>794632</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>954601</t>
+          <t>966083</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -7525,12 +7525,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>13,81%</t>
+          <t>13,98%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>16,79%</t>
+          <t>16,99%</t>
         </is>
       </c>
     </row>
@@ -7553,12 +7553,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>446863</t>
+          <t>443283</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>527397</t>
+          <t>522492</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -7568,12 +7568,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>17,51%</t>
+          <t>17,37%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>20,66%</t>
+          <t>20,47%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -7588,12 +7588,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>499434</t>
+          <t>527623</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>724281</t>
+          <t>726740</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -7603,12 +7603,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>15,94%</t>
+          <t>16,84%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>23,12%</t>
+          <t>23,2%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -7623,12 +7623,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>1021834</t>
+          <t>1002787</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>1220016</t>
+          <t>1217733</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -7638,12 +7638,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>17,97%</t>
+          <t>17,64%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>21,46%</t>
+          <t>21,42%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P39C-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P39C-Habitat-trans_orig.xlsx
@@ -731,12 +731,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>52877</t>
+          <t>51744</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>85159</t>
+          <t>84468</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -746,12 +746,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>10,03%</t>
+          <t>9,81%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>16,15%</t>
+          <t>16,02%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -766,12 +766,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>34319</t>
+          <t>34561</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>59271</t>
+          <t>60395</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -781,12 +781,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>6,09%</t>
+          <t>6,14%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>10,53%</t>
+          <t>10,73%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -801,12 +801,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>95619</t>
+          <t>96321</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>136080</t>
+          <t>138697</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -816,12 +816,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>8,77%</t>
+          <t>8,83%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>12,48%</t>
+          <t>12,72%</t>
         </is>
       </c>
     </row>
@@ -844,12 +844,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>108950</t>
+          <t>108274</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>149277</t>
+          <t>147970</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -859,12 +859,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>20,66%</t>
+          <t>20,53%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>28,31%</t>
+          <t>28,06%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -879,12 +879,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>108399</t>
+          <t>109935</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>147638</t>
+          <t>147399</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -894,12 +894,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>19,25%</t>
+          <t>19,52%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>26,22%</t>
+          <t>26,18%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -914,12 +914,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>227206</t>
+          <t>228926</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>282653</t>
+          <t>286135</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -929,12 +929,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>20,84%</t>
+          <t>20,99%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>25,92%</t>
+          <t>26,24%</t>
         </is>
       </c>
     </row>
@@ -957,12 +957,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>129913</t>
+          <t>132383</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>171738</t>
+          <t>173493</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -972,12 +972,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>24,63%</t>
+          <t>25,1%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>32,56%</t>
+          <t>32,9%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>142239</t>
+          <t>141958</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>184292</t>
+          <t>183467</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>25,26%</t>
+          <t>25,21%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>32,73%</t>
+          <t>32,58%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>281755</t>
+          <t>283074</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>343235</t>
+          <t>341898</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1042,12 +1042,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>25,84%</t>
+          <t>25,96%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>31,48%</t>
+          <t>31,35%</t>
         </is>
       </c>
     </row>
@@ -1070,12 +1070,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>64397</t>
+          <t>64240</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>97849</t>
+          <t>97455</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1085,12 +1085,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>12,21%</t>
+          <t>12,18%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>18,55%</t>
+          <t>18,48%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1105,12 +1105,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>72897</t>
+          <t>70729</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>106022</t>
+          <t>105169</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1120,12 +1120,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>12,95%</t>
+          <t>12,56%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>18,83%</t>
+          <t>18,68%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1140,12 +1140,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>144769</t>
+          <t>143629</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>193545</t>
+          <t>191621</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1155,12 +1155,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>13,28%</t>
+          <t>13,17%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>17,75%</t>
+          <t>17,57%</t>
         </is>
       </c>
     </row>
@@ -1183,12 +1183,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>81077</t>
+          <t>84813</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>117726</t>
+          <t>119024</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1198,12 +1198,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>15,37%</t>
+          <t>16,08%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>22,32%</t>
+          <t>22,57%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1218,12 +1218,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>121093</t>
+          <t>119688</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>163763</t>
+          <t>160502</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1233,12 +1233,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>21,5%</t>
+          <t>21,26%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>29,08%</t>
+          <t>28,5%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1253,12 +1253,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>211157</t>
+          <t>212177</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>269146</t>
+          <t>268555</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1268,12 +1268,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>19,36%</t>
+          <t>19,46%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>24,68%</t>
+          <t>24,63%</t>
         </is>
       </c>
     </row>
@@ -1413,12 +1413,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>93601</t>
+          <t>91756</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>133120</t>
+          <t>133609</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1428,12 +1428,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>11,55%</t>
+          <t>11,32%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>16,42%</t>
+          <t>16,49%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1448,12 +1448,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>78942</t>
+          <t>75827</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>116329</t>
+          <t>115092</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1463,12 +1463,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>8,58%</t>
+          <t>8,24%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>12,64%</t>
+          <t>12,51%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1483,12 +1483,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>179262</t>
+          <t>179275</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>236632</t>
+          <t>234991</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1503,7 +1503,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>13,67%</t>
+          <t>13,58%</t>
         </is>
       </c>
     </row>
@@ -1526,12 +1526,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>174640</t>
+          <t>174324</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>227985</t>
+          <t>223568</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1541,12 +1541,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>21,55%</t>
+          <t>21,51%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>28,13%</t>
+          <t>27,58%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1561,12 +1561,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>217532</t>
+          <t>217923</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>273803</t>
+          <t>271422</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1576,12 +1576,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>23,65%</t>
+          <t>23,69%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>29,76%</t>
+          <t>29,5%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1596,12 +1596,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>404435</t>
+          <t>408682</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>482320</t>
+          <t>481460</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1611,12 +1611,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>23,37%</t>
+          <t>23,62%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>27,87%</t>
+          <t>27,82%</t>
         </is>
       </c>
     </row>
@@ -1639,12 +1639,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>216233</t>
+          <t>217281</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>269122</t>
+          <t>274002</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1654,12 +1654,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>26,68%</t>
+          <t>26,81%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>33,21%</t>
+          <t>33,81%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1674,12 +1674,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>245334</t>
+          <t>245308</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>300490</t>
+          <t>301169</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1689,12 +1689,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>26,67%</t>
+          <t>26,66%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>32,66%</t>
+          <t>32,74%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1709,12 +1709,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>477303</t>
+          <t>479499</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>554062</t>
+          <t>553424</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1724,12 +1724,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>27,58%</t>
+          <t>27,71%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>32,02%</t>
+          <t>31,98%</t>
         </is>
       </c>
     </row>
@@ -1752,12 +1752,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>91772</t>
+          <t>91510</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>133696</t>
+          <t>132801</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1767,12 +1767,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>11,32%</t>
+          <t>11,29%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>16,5%</t>
+          <t>16,39%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1787,12 +1787,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>109687</t>
+          <t>106565</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>152484</t>
+          <t>153030</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1802,12 +1802,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>11,92%</t>
+          <t>11,58%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>16,57%</t>
+          <t>16,63%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1822,12 +1822,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>213944</t>
+          <t>213513</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>274170</t>
+          <t>271469</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1837,12 +1837,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>12,36%</t>
+          <t>12,34%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>15,84%</t>
+          <t>15,69%</t>
         </is>
       </c>
     </row>
@@ -1865,12 +1865,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>124049</t>
+          <t>122716</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>168127</t>
+          <t>169314</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1880,12 +1880,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>15,31%</t>
+          <t>15,14%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>20,74%</t>
+          <t>20,89%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1900,12 +1900,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>152148</t>
+          <t>155345</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>203353</t>
+          <t>205816</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1915,12 +1915,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>16,54%</t>
+          <t>16,89%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>22,1%</t>
+          <t>22,37%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1935,12 +1935,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>292689</t>
+          <t>292892</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>357195</t>
+          <t>359653</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1950,12 +1950,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>16,91%</t>
+          <t>16,93%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>20,64%</t>
+          <t>20,78%</t>
         </is>
       </c>
     </row>
@@ -2095,12 +2095,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>39236</t>
+          <t>38697</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>67871</t>
+          <t>69058</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2110,12 +2110,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>6,79%</t>
+          <t>6,7%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>11,75%</t>
+          <t>11,96%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2130,12 +2130,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>39004</t>
+          <t>38709</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>66340</t>
+          <t>66008</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2145,12 +2145,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>5,84%</t>
+          <t>5,79%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>9,93%</t>
+          <t>9,88%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2165,12 +2165,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>84314</t>
+          <t>82634</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>123759</t>
+          <t>124112</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>6,77%</t>
+          <t>6,63%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>9,94%</t>
+          <t>9,96%</t>
         </is>
       </c>
     </row>
@@ -2208,12 +2208,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>167461</t>
+          <t>167380</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>213683</t>
+          <t>214082</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2223,12 +2223,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>28,99%</t>
+          <t>28,98%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>37,0%</t>
+          <t>37,07%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2243,12 +2243,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>155873</t>
+          <t>156411</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>200536</t>
+          <t>202492</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2258,12 +2258,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>23,33%</t>
+          <t>23,41%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>30,02%</t>
+          <t>30,31%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2278,12 +2278,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>335719</t>
+          <t>332340</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>403619</t>
+          <t>399827</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2293,12 +2293,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>26,95%</t>
+          <t>26,68%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>32,4%</t>
+          <t>32,1%</t>
         </is>
       </c>
     </row>
@@ -2321,12 +2321,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>156224</t>
+          <t>157625</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>202338</t>
+          <t>203731</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2336,12 +2336,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>27,05%</t>
+          <t>27,29%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>35,03%</t>
+          <t>35,27%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2356,12 +2356,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>203866</t>
+          <t>203959</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>253736</t>
+          <t>254168</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2371,12 +2371,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>30,51%</t>
+          <t>30,53%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>37,98%</t>
+          <t>38,04%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2391,12 +2391,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>374213</t>
+          <t>374870</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>441109</t>
+          <t>443577</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2406,12 +2406,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>30,04%</t>
+          <t>30,09%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>35,41%</t>
+          <t>35,61%</t>
         </is>
       </c>
     </row>
@@ -2434,12 +2434,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>51373</t>
+          <t>51508</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>84952</t>
+          <t>82863</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>8,89%</t>
+          <t>8,92%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>14,71%</t>
+          <t>14,35%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2469,12 +2469,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>57053</t>
+          <t>59793</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>94697</t>
+          <t>92529</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2484,12 +2484,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>8,54%</t>
+          <t>8,95%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>14,17%</t>
+          <t>13,85%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2504,12 +2504,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>119134</t>
+          <t>118203</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>166459</t>
+          <t>168080</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2519,12 +2519,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>9,56%</t>
+          <t>9,49%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>13,36%</t>
+          <t>13,49%</t>
         </is>
       </c>
     </row>
@@ -2547,12 +2547,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>73046</t>
+          <t>73737</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>111391</t>
+          <t>109949</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2562,12 +2562,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>12,65%</t>
+          <t>12,77%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>19,29%</t>
+          <t>19,04%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2582,12 +2582,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>116118</t>
+          <t>113649</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>159567</t>
+          <t>157762</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2597,12 +2597,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>17,38%</t>
+          <t>17,01%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>23,88%</t>
+          <t>23,61%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2617,12 +2617,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>201997</t>
+          <t>201237</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>258152</t>
+          <t>259850</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2632,12 +2632,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>16,22%</t>
+          <t>16,15%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>20,72%</t>
+          <t>20,86%</t>
         </is>
       </c>
     </row>
@@ -2777,12 +2777,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>66653</t>
+          <t>66422</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>100923</t>
+          <t>100568</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2792,12 +2792,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>9,21%</t>
+          <t>9,18%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>13,95%</t>
+          <t>13,9%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2812,12 +2812,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>45873</t>
+          <t>46154</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>76407</t>
+          <t>75418</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2827,12 +2827,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>5,36%</t>
+          <t>5,39%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>8,93%</t>
+          <t>8,81%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2847,12 +2847,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>118314</t>
+          <t>121247</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>165037</t>
+          <t>165441</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2862,12 +2862,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>7,49%</t>
+          <t>7,68%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>10,45%</t>
+          <t>10,47%</t>
         </is>
       </c>
     </row>
@@ -2890,12 +2890,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>185949</t>
+          <t>186031</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>233155</t>
+          <t>233082</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2905,12 +2905,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>25,7%</t>
+          <t>25,71%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>32,23%</t>
+          <t>32,22%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2925,12 +2925,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>202383</t>
+          <t>203701</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>257240</t>
+          <t>257306</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2940,12 +2940,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>23,65%</t>
+          <t>23,8%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>30,05%</t>
+          <t>30,06%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2960,12 +2960,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>401473</t>
+          <t>402360</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>475029</t>
+          <t>477115</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2975,12 +2975,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>25,42%</t>
+          <t>25,48%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>30,08%</t>
+          <t>30,21%</t>
         </is>
       </c>
     </row>
@@ -3003,12 +3003,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>168882</t>
+          <t>170135</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>216908</t>
+          <t>217780</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3018,12 +3018,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>23,34%</t>
+          <t>23,52%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>29,98%</t>
+          <t>30,1%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3038,12 +3038,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>224799</t>
+          <t>225680</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>282994</t>
+          <t>281630</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3053,12 +3053,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>26,26%</t>
+          <t>26,37%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>33,06%</t>
+          <t>32,9%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3073,12 +3073,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>409914</t>
+          <t>412273</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>482583</t>
+          <t>485784</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3088,12 +3088,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>25,95%</t>
+          <t>26,1%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>30,56%</t>
+          <t>30,76%</t>
         </is>
       </c>
     </row>
@@ -3116,12 +3116,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>88349</t>
+          <t>90196</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>128272</t>
+          <t>125733</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3131,12 +3131,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>12,21%</t>
+          <t>12,47%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>17,73%</t>
+          <t>17,38%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3151,12 +3151,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>116098</t>
+          <t>117891</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>161498</t>
+          <t>160397</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3166,12 +3166,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>13,56%</t>
+          <t>13,77%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>18,87%</t>
+          <t>18,74%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3186,12 +3186,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>214184</t>
+          <t>217742</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>274519</t>
+          <t>276103</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3201,12 +3201,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>13,56%</t>
+          <t>13,79%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>17,38%</t>
+          <t>17,48%</t>
         </is>
       </c>
     </row>
@@ -3229,12 +3229,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>113936</t>
+          <t>113827</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>155726</t>
+          <t>153266</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3244,12 +3244,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>15,75%</t>
+          <t>15,73%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>21,52%</t>
+          <t>21,18%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3264,12 +3264,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>151152</t>
+          <t>150943</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>203820</t>
+          <t>200778</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3279,12 +3279,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>17,66%</t>
+          <t>17,64%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>23,81%</t>
+          <t>23,46%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3299,12 +3299,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>278104</t>
+          <t>279343</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>342171</t>
+          <t>343853</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3314,12 +3314,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>17,61%</t>
+          <t>17,69%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>21,66%</t>
+          <t>21,77%</t>
         </is>
       </c>
     </row>
@@ -3459,12 +3459,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>279654</t>
+          <t>278571</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>348754</t>
+          <t>346149</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3474,12 +3474,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>10,6%</t>
+          <t>10,56%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>13,22%</t>
+          <t>13,12%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3494,12 +3494,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>221359</t>
+          <t>223808</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>283908</t>
+          <t>282967</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3509,12 +3509,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>7,36%</t>
+          <t>7,44%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>9,44%</t>
+          <t>9,41%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3529,12 +3529,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>521810</t>
+          <t>521245</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>612555</t>
+          <t>610434</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3544,12 +3544,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>9,24%</t>
+          <t>9,23%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>10,85%</t>
+          <t>10,81%</t>
         </is>
       </c>
     </row>
@@ -3572,12 +3572,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>680428</t>
+          <t>680430</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>773753</t>
+          <t>772857</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3592,7 +3592,7 @@
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>29,32%</t>
+          <t>29,29%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3607,12 +3607,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>732802</t>
+          <t>731722</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>830799</t>
+          <t>828586</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3622,12 +3622,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>24,37%</t>
+          <t>24,33%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>27,63%</t>
+          <t>27,55%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3642,12 +3642,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>1438837</t>
+          <t>1439271</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>1572458</t>
+          <t>1573771</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3657,12 +3657,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>25,48%</t>
+          <t>25,49%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>27,85%</t>
+          <t>27,87%</t>
         </is>
       </c>
     </row>
@@ -3685,12 +3685,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>720362</t>
+          <t>722238</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>815338</t>
+          <t>820541</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3700,12 +3700,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>27,3%</t>
+          <t>27,37%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>30,9%</t>
+          <t>31,09%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3720,12 +3720,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>865861</t>
+          <t>864666</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>964915</t>
+          <t>961592</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3735,12 +3735,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>28,79%</t>
+          <t>28,75%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>32,09%</t>
+          <t>31,98%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3755,12 +3755,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>1613853</t>
+          <t>1615897</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>1752680</t>
+          <t>1762044</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3770,12 +3770,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>28,58%</t>
+          <t>28,62%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>31,04%</t>
+          <t>31,21%</t>
         </is>
       </c>
     </row>
@@ -3798,12 +3798,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>330688</t>
+          <t>328465</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>404019</t>
+          <t>399353</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3813,12 +3813,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>12,53%</t>
+          <t>12,45%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>15,31%</t>
+          <t>15,13%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3833,12 +3833,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>389115</t>
+          <t>393375</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>470399</t>
+          <t>470133</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3848,12 +3848,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>12,94%</t>
+          <t>13,08%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>15,64%</t>
+          <t>15,63%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3868,12 +3868,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>740085</t>
+          <t>744716</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>846161</t>
+          <t>851703</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3883,12 +3883,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>13,11%</t>
+          <t>13,19%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>14,99%</t>
+          <t>15,09%</t>
         </is>
       </c>
     </row>
@@ -3911,12 +3911,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>432030</t>
+          <t>427808</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>510298</t>
+          <t>510365</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3926,7 +3926,7 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>16,37%</t>
+          <t>16,21%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
@@ -3946,12 +3946,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>585361</t>
+          <t>585189</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>677930</t>
+          <t>673185</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3961,12 +3961,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>19,47%</t>
+          <t>19,46%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>22,54%</t>
+          <t>22,39%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3981,12 +3981,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>1040577</t>
+          <t>1038781</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>1165572</t>
+          <t>1163154</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -3996,12 +3996,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>18,43%</t>
+          <t>18,4%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>20,64%</t>
+          <t>20,6%</t>
         </is>
       </c>
     </row>
@@ -4368,32 +4368,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>49163</t>
+          <t>56123</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>37092</t>
+          <t>40917</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>66552</t>
+          <t>72838</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>9,07%</t>
+          <t>9,59%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>6,84%</t>
+          <t>6,99%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>12,28%</t>
+          <t>12,44%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4403,32 +4403,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>62060</t>
+          <t>66061</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>50271</t>
+          <t>53526</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>78001</t>
+          <t>81611</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>10,06%</t>
+          <t>9,97%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>8,15%</t>
+          <t>8,08%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>12,65%</t>
+          <t>12,31%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4438,32 +4438,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>111224</t>
+          <t>122185</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>92143</t>
+          <t>101327</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>132811</t>
+          <t>144409</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>9,6%</t>
+          <t>9,79%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>7,95%</t>
+          <t>8,12%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>11,46%</t>
+          <t>11,57%</t>
         </is>
       </c>
     </row>
@@ -4481,32 +4481,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>128100</t>
+          <t>134408</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>108149</t>
+          <t>113579</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>148244</t>
+          <t>156596</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>23,63%</t>
+          <t>22,96%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>19,95%</t>
+          <t>19,4%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>27,35%</t>
+          <t>26,75%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4516,32 +4516,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>123697</t>
+          <t>131406</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>108974</t>
+          <t>115455</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>140998</t>
+          <t>149571</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>20,06%</t>
+          <t>19,83%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>17,67%</t>
+          <t>17,42%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>22,86%</t>
+          <t>22,57%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4551,32 +4551,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>251798</t>
+          <t>265813</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>226452</t>
+          <t>239773</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>278921</t>
+          <t>294569</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>21,73%</t>
+          <t>21,3%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>19,54%</t>
+          <t>19,21%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>24,07%</t>
+          <t>23,6%</t>
         </is>
       </c>
     </row>
@@ -4594,32 +4594,32 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>143228</t>
+          <t>153218</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>123249</t>
+          <t>132705</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>166471</t>
+          <t>175335</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>26,42%</t>
+          <t>26,17%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>22,74%</t>
+          <t>22,67%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>30,71%</t>
+          <t>29,95%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -4629,32 +4629,32 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>159768</t>
+          <t>175841</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>143759</t>
+          <t>158494</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>178636</t>
+          <t>196793</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>25,91%</t>
+          <t>26,53%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>23,31%</t>
+          <t>23,91%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>28,96%</t>
+          <t>29,69%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -4664,32 +4664,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>302995</t>
+          <t>329059</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>277110</t>
+          <t>302496</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>329137</t>
+          <t>357472</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>26,15%</t>
+          <t>26,36%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>23,91%</t>
+          <t>24,23%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>28,4%</t>
+          <t>28,64%</t>
         </is>
       </c>
     </row>
@@ -4707,32 +4707,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>105274</t>
+          <t>116402</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>89046</t>
+          <t>97666</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>124144</t>
+          <t>138293</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>19,42%</t>
+          <t>19,88%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>16,43%</t>
+          <t>16,68%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>22,9%</t>
+          <t>23,62%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4742,32 +4742,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>116578</t>
+          <t>124853</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>102109</t>
+          <t>111492</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>132224</t>
+          <t>143179</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>18,9%</t>
+          <t>18,84%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>16,56%</t>
+          <t>16,82%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>21,44%</t>
+          <t>21,6%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4777,32 +4777,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>221852</t>
+          <t>241256</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>200467</t>
+          <t>217759</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>243560</t>
+          <t>272316</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>19,15%</t>
+          <t>19,33%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>17,3%</t>
+          <t>17,45%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>21,02%</t>
+          <t>21,82%</t>
         </is>
       </c>
     </row>
@@ -4820,32 +4820,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>116265</t>
+          <t>125268</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>99911</t>
+          <t>106790</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>136163</t>
+          <t>144660</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>21,45%</t>
+          <t>21,4%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>18,43%</t>
+          <t>18,24%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>25,12%</t>
+          <t>24,71%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4855,32 +4855,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>154637</t>
+          <t>164632</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>138113</t>
+          <t>146998</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>172010</t>
+          <t>183018</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>25,07%</t>
+          <t>24,84%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>22,39%</t>
+          <t>22,18%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>27,89%</t>
+          <t>27,61%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4890,32 +4890,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>270901</t>
+          <t>289900</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>245554</t>
+          <t>266283</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>296813</t>
+          <t>318062</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>23,38%</t>
+          <t>23,23%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>21,19%</t>
+          <t>21,33%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>25,61%</t>
+          <t>25,48%</t>
         </is>
       </c>
     </row>
@@ -4933,17 +4933,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>542030</t>
+          <t>585419</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>542030</t>
+          <t>585419</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>542030</t>
+          <t>585419</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -4968,17 +4968,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>616740</t>
+          <t>662793</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>616740</t>
+          <t>662793</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>616740</t>
+          <t>662793</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -5003,17 +5003,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>1158770</t>
+          <t>1248212</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>1158770</t>
+          <t>1248212</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>1158770</t>
+          <t>1248212</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -5050,32 +5050,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>72364</t>
+          <t>78482</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>56917</t>
+          <t>62431</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>92272</t>
+          <t>97437</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>10,1%</t>
+          <t>10,0%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>7,94%</t>
+          <t>7,95%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>12,87%</t>
+          <t>12,41%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5085,32 +5085,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>56289</t>
+          <t>61441</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>44512</t>
+          <t>46896</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>69934</t>
+          <t>75889</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>6,98%</t>
+          <t>6,86%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>5,52%</t>
+          <t>5,23%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>8,67%</t>
+          <t>8,47%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5120,32 +5120,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>128653</t>
+          <t>139923</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>105602</t>
+          <t>118733</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>151453</t>
+          <t>165402</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>8,45%</t>
+          <t>8,32%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>6,93%</t>
+          <t>7,06%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>9,94%</t>
+          <t>9,84%</t>
         </is>
       </c>
     </row>
@@ -5163,32 +5163,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>156101</t>
+          <t>179178</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>134006</t>
+          <t>154546</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>179748</t>
+          <t>204997</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>21,78%</t>
+          <t>22,83%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>18,7%</t>
+          <t>19,69%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>25,08%</t>
+          <t>26,11%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -5198,32 +5198,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>199579</t>
+          <t>223192</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>180353</t>
+          <t>202628</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>224336</t>
+          <t>248063</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>24,75%</t>
+          <t>24,91%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>22,36%</t>
+          <t>22,61%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>27,82%</t>
+          <t>27,68%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5233,32 +5233,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>355679</t>
+          <t>402369</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>323635</t>
+          <t>368344</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>386311</t>
+          <t>438695</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>23,35%</t>
+          <t>23,93%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>21,25%</t>
+          <t>21,91%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>25,36%</t>
+          <t>26,09%</t>
         </is>
       </c>
     </row>
@@ -5276,32 +5276,32 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>230320</t>
+          <t>246747</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>203247</t>
+          <t>220093</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>258498</t>
+          <t>280214</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>32,13%</t>
+          <t>31,43%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>28,36%</t>
+          <t>28,04%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>36,06%</t>
+          <t>35,7%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -5311,32 +5311,32 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>220541</t>
+          <t>247443</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>199221</t>
+          <t>227410</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>240702</t>
+          <t>269570</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>27,35%</t>
+          <t>27,61%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>24,7%</t>
+          <t>25,38%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>29,85%</t>
+          <t>30,08%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -5346,32 +5346,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>450861</t>
+          <t>494191</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>418913</t>
+          <t>459417</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>488498</t>
+          <t>530422</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>29,6%</t>
+          <t>29,4%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>27,5%</t>
+          <t>27,33%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>32,07%</t>
+          <t>31,55%</t>
         </is>
       </c>
     </row>
@@ -5389,32 +5389,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>118397</t>
+          <t>128018</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>99287</t>
+          <t>108068</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>140240</t>
+          <t>152611</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>16,52%</t>
+          <t>16,31%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>13,85%</t>
+          <t>13,77%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>19,56%</t>
+          <t>19,44%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5424,32 +5424,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>131918</t>
+          <t>146371</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>116668</t>
+          <t>129413</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>149749</t>
+          <t>166488</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>16,36%</t>
+          <t>16,33%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>14,47%</t>
+          <t>14,44%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>18,57%</t>
+          <t>18,58%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5459,32 +5459,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>250316</t>
+          <t>274389</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>223414</t>
+          <t>246387</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>279135</t>
+          <t>302184</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>16,43%</t>
+          <t>16,32%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>14,67%</t>
+          <t>14,66%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>18,33%</t>
+          <t>17,97%</t>
         </is>
       </c>
     </row>
@@ -5502,32 +5502,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>139608</t>
+          <t>152579</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>119273</t>
+          <t>130888</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>161151</t>
+          <t>174882</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>19,48%</t>
+          <t>19,44%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>16,64%</t>
+          <t>16,67%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>22,48%</t>
+          <t>22,28%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5537,32 +5537,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>198084</t>
+          <t>217705</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>177301</t>
+          <t>193387</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>219594</t>
+          <t>240981</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>24,56%</t>
+          <t>24,29%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>21,99%</t>
+          <t>21,58%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>27,23%</t>
+          <t>26,89%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5572,32 +5572,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>337692</t>
+          <t>370285</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>307752</t>
+          <t>338503</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>371835</t>
+          <t>405063</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>22,17%</t>
+          <t>22,03%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>20,2%</t>
+          <t>20,14%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>24,41%</t>
+          <t>24,09%</t>
         </is>
       </c>
     </row>
@@ -5615,17 +5615,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>716790</t>
+          <t>785004</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>716790</t>
+          <t>785004</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>716790</t>
+          <t>785004</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -5650,17 +5650,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>806411</t>
+          <t>896153</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>806411</t>
+          <t>896153</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>806411</t>
+          <t>896153</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -5685,17 +5685,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>1523201</t>
+          <t>1681157</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>1523201</t>
+          <t>1681157</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>1523201</t>
+          <t>1681157</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -5732,32 +5732,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>50779</t>
+          <t>59636</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>36410</t>
+          <t>43229</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>71591</t>
+          <t>80313</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>9,14%</t>
+          <t>9,54%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>6,56%</t>
+          <t>6,92%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>12,89%</t>
+          <t>12,85%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5767,32 +5767,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>44719</t>
+          <t>49518</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>20012</t>
+          <t>38975</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>64748</t>
+          <t>62415</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>5,4%</t>
+          <t>7,19%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>2,42%</t>
+          <t>5,66%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>7,82%</t>
+          <t>9,06%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5802,32 +5802,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>95498</t>
+          <t>109154</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>56972</t>
+          <t>88632</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>124064</t>
+          <t>132550</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>6,9%</t>
+          <t>8,31%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>4,12%</t>
+          <t>6,75%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>8,97%</t>
+          <t>10,09%</t>
         </is>
       </c>
     </row>
@@ -5845,32 +5845,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>192461</t>
+          <t>213809</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>168340</t>
+          <t>188795</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>217314</t>
+          <t>241308</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>34,66%</t>
+          <t>34,22%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>30,31%</t>
+          <t>30,22%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>39,13%</t>
+          <t>38,62%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5880,32 +5880,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>182531</t>
+          <t>210219</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>82173</t>
+          <t>189669</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>254599</t>
+          <t>233138</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>22,04%</t>
+          <t>30,51%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>9,92%</t>
+          <t>27,52%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>30,74%</t>
+          <t>33,83%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5915,32 +5915,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>374992</t>
+          <t>424028</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>225906</t>
+          <t>390528</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>458315</t>
+          <t>460131</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>27,1%</t>
+          <t>32,27%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>16,33%</t>
+          <t>29,72%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>33,12%</t>
+          <t>35,02%</t>
         </is>
       </c>
     </row>
@@ -5958,32 +5958,32 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>152670</t>
+          <t>169472</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>130773</t>
+          <t>144909</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>176613</t>
+          <t>193551</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>27,49%</t>
+          <t>27,12%</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>23,55%</t>
+          <t>23,19%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>31,8%</t>
+          <t>30,98%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -5993,32 +5993,32 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>415776</t>
+          <t>202839</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>262759</t>
+          <t>182005</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>644720</t>
+          <t>225720</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>50,19%</t>
+          <t>29,43%</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>31,72%</t>
+          <t>26,41%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>77,83%</t>
+          <t>32,75%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -6028,32 +6028,32 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>568446</t>
+          <t>372311</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>401469</t>
+          <t>339474</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>887333</t>
+          <t>402504</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>41,08%</t>
+          <t>28,34%</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>29,01%</t>
+          <t>25,84%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>64,13%</t>
+          <t>30,63%</t>
         </is>
       </c>
     </row>
@@ -6071,22 +6071,22 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>69600</t>
+          <t>79057</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>55618</t>
+          <t>62626</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>88778</t>
+          <t>98276</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>12,53%</t>
+          <t>12,65%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
@@ -6096,7 +6096,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>15,99%</t>
+          <t>15,73%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -6106,32 +6106,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>72448</t>
+          <t>91197</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>34064</t>
+          <t>76696</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>103576</t>
+          <t>107217</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>8,75%</t>
+          <t>13,23%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>4,11%</t>
+          <t>11,13%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>12,5%</t>
+          <t>15,56%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -6141,32 +6141,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>142047</t>
+          <t>170255</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>84623</t>
+          <t>148319</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>179665</t>
+          <t>196825</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>10,27%</t>
+          <t>12,96%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>6,12%</t>
+          <t>11,29%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>12,98%</t>
+          <t>14,98%</t>
         </is>
       </c>
     </row>
@@ -6184,32 +6184,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>89816</t>
+          <t>102822</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>73294</t>
+          <t>85780</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>108190</t>
+          <t>123025</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>16,17%</t>
+          <t>16,46%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>13,2%</t>
+          <t>13,73%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>19,48%</t>
+          <t>19,69%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -6219,32 +6219,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>112884</t>
+          <t>135347</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>51599</t>
+          <t>117268</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>157862</t>
+          <t>154159</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>13,63%</t>
+          <t>19,64%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>6,23%</t>
+          <t>17,02%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>19,06%</t>
+          <t>22,37%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -6254,32 +6254,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>202700</t>
+          <t>238169</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>128652</t>
+          <t>211069</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>249390</t>
+          <t>263615</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>14,65%</t>
+          <t>18,13%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>9,3%</t>
+          <t>16,06%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>18,02%</t>
+          <t>20,06%</t>
         </is>
       </c>
     </row>
@@ -6297,17 +6297,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>555327</t>
+          <t>624795</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>555327</t>
+          <t>624795</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>555327</t>
+          <t>624795</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -6332,17 +6332,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>828357</t>
+          <t>689120</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>828357</t>
+          <t>689120</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>828357</t>
+          <t>689120</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -6367,17 +6367,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>1383684</t>
+          <t>1313916</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>1383684</t>
+          <t>1313916</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>1383684</t>
+          <t>1313916</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -6414,32 +6414,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>47145</t>
+          <t>53800</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>35110</t>
+          <t>40941</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>63289</t>
+          <t>70784</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>6,39%</t>
+          <t>6,94%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>4,76%</t>
+          <t>5,28%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>8,57%</t>
+          <t>9,14%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6449,32 +6449,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>51613</t>
+          <t>54418</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>40615</t>
+          <t>41447</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>64781</t>
+          <t>69729</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>5,86%</t>
+          <t>5,72%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>4,61%</t>
+          <t>4,35%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>7,35%</t>
+          <t>7,32%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6484,32 +6484,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>98758</t>
+          <t>108219</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>80803</t>
+          <t>89876</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>119012</t>
+          <t>126822</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>6,1%</t>
+          <t>6,27%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>4,99%</t>
+          <t>5,2%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>7,35%</t>
+          <t>7,34%</t>
         </is>
       </c>
     </row>
@@ -6527,32 +6527,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>192207</t>
+          <t>203916</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>166692</t>
+          <t>178123</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>219809</t>
+          <t>228101</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>26,04%</t>
+          <t>26,32%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>22,58%</t>
+          <t>22,99%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>29,78%</t>
+          <t>29,44%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -6562,32 +6562,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>193961</t>
+          <t>210863</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>175302</t>
+          <t>192081</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>215457</t>
+          <t>236235</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>22,01%</t>
+          <t>22,15%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>19,89%</t>
+          <t>20,17%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>24,44%</t>
+          <t>24,81%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -6597,32 +6597,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>386168</t>
+          <t>414779</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>353069</t>
+          <t>381098</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>420853</t>
+          <t>451862</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>23,84%</t>
+          <t>24,02%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>21,8%</t>
+          <t>22,07%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>25,99%</t>
+          <t>26,17%</t>
         </is>
       </c>
     </row>
@@ -6640,32 +6640,32 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>228654</t>
+          <t>238651</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>204310</t>
+          <t>213471</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>253575</t>
+          <t>266309</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>30,98%</t>
+          <t>30,8%</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>27,68%</t>
+          <t>27,55%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>34,35%</t>
+          <t>34,38%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -6675,32 +6675,32 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>288144</t>
+          <t>308520</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>266599</t>
+          <t>283881</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>311518</t>
+          <t>335219</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>32,69%</t>
+          <t>32,4%</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>30,25%</t>
+          <t>29,82%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>35,34%</t>
+          <t>35,21%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -6710,32 +6710,32 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>516798</t>
+          <t>547171</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>482355</t>
+          <t>513013</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>553269</t>
+          <t>583162</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t>31,91%</t>
+          <t>31,69%</t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>29,78%</t>
+          <t>29,71%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>34,16%</t>
+          <t>33,77%</t>
         </is>
       </c>
     </row>
@@ -6753,32 +6753,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>132393</t>
+          <t>139159</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>113367</t>
+          <t>118882</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>155130</t>
+          <t>162682</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>17,94%</t>
+          <t>17,96%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>15,36%</t>
+          <t>15,35%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>21,02%</t>
+          <t>21,0%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6788,32 +6788,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>150268</t>
+          <t>161789</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>134105</t>
+          <t>143411</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>171907</t>
+          <t>180858</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>17,05%</t>
+          <t>16,99%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>15,21%</t>
+          <t>15,06%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>19,5%</t>
+          <t>19,0%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6823,32 +6823,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>282661</t>
+          <t>300948</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>257327</t>
+          <t>274138</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>314330</t>
+          <t>332763</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>17,45%</t>
+          <t>17,43%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>15,89%</t>
+          <t>15,88%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>19,41%</t>
+          <t>19,27%</t>
         </is>
       </c>
     </row>
@@ -6866,32 +6866,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>137737</t>
+          <t>139188</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>118538</t>
+          <t>118862</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>159990</t>
+          <t>160559</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>18,66%</t>
+          <t>17,97%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>16,06%</t>
+          <t>15,34%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>21,67%</t>
+          <t>20,72%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6901,32 +6901,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>197448</t>
+          <t>216512</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>177137</t>
+          <t>195705</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>218822</t>
+          <t>241895</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>22,4%</t>
+          <t>22,74%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>20,1%</t>
+          <t>20,56%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>24,83%</t>
+          <t>25,41%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6936,32 +6936,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>335185</t>
+          <t>355700</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>308239</t>
+          <t>325538</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>366668</t>
+          <t>385622</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>20,7%</t>
+          <t>20,6%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>19,03%</t>
+          <t>18,85%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>22,64%</t>
+          <t>22,33%</t>
         </is>
       </c>
     </row>
@@ -6979,17 +6979,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>738136</t>
+          <t>774715</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>738136</t>
+          <t>774715</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>738136</t>
+          <t>774715</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -7014,17 +7014,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>881434</t>
+          <t>952102</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>881434</t>
+          <t>952102</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>881434</t>
+          <t>952102</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -7049,17 +7049,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>1619570</t>
+          <t>1726818</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>1619570</t>
+          <t>1726818</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>1619570</t>
+          <t>1726818</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -7096,32 +7096,32 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>219452</t>
+          <t>248042</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>189985</t>
+          <t>213635</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>253249</t>
+          <t>282025</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>8,6%</t>
+          <t>8,95%</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>7,44%</t>
+          <t>7,71%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>9,92%</t>
+          <t>10,18%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -7131,32 +7131,32 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>214681</t>
+          <t>231439</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>169140</t>
+          <t>206786</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>245341</t>
+          <t>258619</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>6,85%</t>
+          <t>7,23%</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>5,4%</t>
+          <t>6,46%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>7,83%</t>
+          <t>8,08%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -7166,32 +7166,32 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>434133</t>
+          <t>479481</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>376305</t>
+          <t>439419</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>477555</t>
+          <t>525776</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t>7,64%</t>
+          <t>8,03%</t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>6,62%</t>
+          <t>7,36%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>8,4%</t>
+          <t>8,81%</t>
         </is>
       </c>
     </row>
@@ -7209,32 +7209,32 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>668869</t>
+          <t>731310</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>624114</t>
+          <t>688161</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>719194</t>
+          <t>781603</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>26,21%</t>
+          <t>26,4%</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>24,45%</t>
+          <t>24,84%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>28,18%</t>
+          <t>28,22%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -7244,32 +7244,32 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>699768</t>
+          <t>775679</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>514877</t>
+          <t>734943</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>764924</t>
+          <t>822304</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>22,34%</t>
+          <t>24,24%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>16,43%</t>
+          <t>22,97%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>24,42%</t>
+          <t>25,7%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -7279,32 +7279,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>1368637</t>
+          <t>1506990</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>1198206</t>
+          <t>1439289</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>1452035</t>
+          <t>1574921</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>24,07%</t>
+          <t>25,24%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>21,08%</t>
+          <t>24,11%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>25,54%</t>
+          <t>26,38%</t>
         </is>
       </c>
     </row>
@@ -7322,32 +7322,32 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>754872</t>
+          <t>808088</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>709204</t>
+          <t>758096</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>807642</t>
+          <t>858923</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>29,58%</t>
+          <t>29,17%</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>27,79%</t>
+          <t>27,37%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>31,64%</t>
+          <t>31,01%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -7357,32 +7357,32 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>1084229</t>
+          <t>934644</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>917760</t>
+          <t>890895</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>1561249</t>
+          <t>977844</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>34,61%</t>
+          <t>29,21%</t>
         </is>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>29,29%</t>
+          <t>27,84%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>49,83%</t>
+          <t>30,56%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -7392,32 +7392,32 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>1839101</t>
+          <t>1742732</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>1666576</t>
+          <t>1678391</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>2360790</t>
+          <t>1814012</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
         <is>
-          <t>32,35%</t>
+          <t>29,19%</t>
         </is>
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>29,31%</t>
+          <t>28,11%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>41,53%</t>
+          <t>30,38%</t>
         </is>
       </c>
     </row>
@@ -7435,22 +7435,22 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>425664</t>
+          <t>462637</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>388860</t>
+          <t>422086</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>465000</t>
+          <t>507319</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>16,68%</t>
+          <t>16,7%</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
@@ -7460,7 +7460,7 @@
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>18,22%</t>
+          <t>18,32%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -7470,32 +7470,32 @@
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>471211</t>
+          <t>524211</t>
         </is>
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>371900</t>
+          <t>491429</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>521615</t>
+          <t>561460</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
-          <t>15,04%</t>
+          <t>16,38%</t>
         </is>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>11,87%</t>
+          <t>15,36%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>16,65%</t>
+          <t>17,54%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -7505,32 +7505,32 @@
       </c>
       <c r="R31" s="2" t="inlineStr">
         <is>
-          <t>896876</t>
+          <t>986847</t>
         </is>
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>794632</t>
+          <t>937906</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>966083</t>
+          <t>1043420</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
         <is>
-          <t>15,78%</t>
+          <t>16,53%</t>
         </is>
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>13,98%</t>
+          <t>15,71%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>16,99%</t>
+          <t>17,48%</t>
         </is>
       </c>
     </row>
@@ -7548,32 +7548,32 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>483425</t>
+          <t>519857</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>443283</t>
+          <t>477579</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>522492</t>
+          <t>562589</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>18,94%</t>
+          <t>18,77%</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>17,37%</t>
+          <t>17,24%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>20,47%</t>
+          <t>20,31%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -7583,32 +7583,32 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>663053</t>
+          <t>734196</t>
         </is>
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>527623</t>
+          <t>691994</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>726740</t>
+          <t>772919</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t>21,16%</t>
+          <t>22,94%</t>
         </is>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>16,84%</t>
+          <t>21,62%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>23,2%</t>
+          <t>24,15%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -7618,32 +7618,32 @@
       </c>
       <c r="R32" s="2" t="inlineStr">
         <is>
-          <t>1146478</t>
+          <t>1254053</t>
         </is>
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>1002787</t>
+          <t>1199179</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>1217733</t>
+          <t>1316351</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
         <is>
-          <t>20,17%</t>
+          <t>21,01%</t>
         </is>
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>17,64%</t>
+          <t>20,09%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>21,42%</t>
+          <t>22,05%</t>
         </is>
       </c>
     </row>
@@ -7661,17 +7661,17 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>2552282</t>
+          <t>2769934</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>2552282</t>
+          <t>2769934</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>2552282</t>
+          <t>2769934</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -7696,17 +7696,17 @@
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>3132942</t>
+          <t>3200169</t>
         </is>
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>3132942</t>
+          <t>3200169</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>3132942</t>
+          <t>3200169</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -7731,17 +7731,17 @@
       </c>
       <c r="R33" s="2" t="inlineStr">
         <is>
-          <t>5685225</t>
+          <t>5970103</t>
         </is>
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>5685225</t>
+          <t>5970103</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>5685225</t>
+          <t>5970103</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
